--- a/output/pdf_financials_xlsx/EDM.xlsx
+++ b/output/pdf_financials_xlsx/EDM.xlsx
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>8.909124</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>10.818928</v>
@@ -19163,7 +19163,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="n">
         <v>8.909124</v>
       </c>

--- a/output/pdf_financials_xlsx/EDM.xlsx
+++ b/output/pdf_financials_xlsx/EDM.xlsx
@@ -1002,46 +1002,46 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.059673</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.248243</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.09715</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.07775700000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.057766</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.055822</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.022023</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.075432</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.035324</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.035265</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.035665</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.048677</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.353125</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.137814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,46 +1870,46 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-29.099952</v>
+        <v>-29.040279</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-14.352883</v>
+        <v>-14.10464</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.684654</v>
+        <v>-1.781804</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.853048</v>
+        <v>-1.930805</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.973618</v>
+        <v>-1.031384</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.262016</v>
+        <v>-1.317838</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.624284</v>
+        <v>-1.646307</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.49296</v>
+        <v>-1.568392</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-7.46286</v>
+        <v>-7.498184</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.352465</v>
+        <v>-1.38773</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.926075</v>
+        <v>-1.96174</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.351037</v>
+        <v>-2.399714</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.920078</v>
+        <v>-2.273203</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.73978</v>
+        <v>-0.877594</v>
       </c>
     </row>
     <row r="28">
@@ -1978,46 +1978,46 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-29.099952</v>
+        <v>-29.040279</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-14.352883</v>
+        <v>-14.10464</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.684654</v>
+        <v>-1.781804</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.853048</v>
+        <v>-1.930805</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.973618</v>
+        <v>-1.031384</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.262016</v>
+        <v>-1.317838</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.624284</v>
+        <v>-1.646307</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.49296</v>
+        <v>-1.568392</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.46286</v>
+        <v>-7.498184</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.352465</v>
+        <v>-1.38773</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.926075</v>
+        <v>-1.96174</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.351037</v>
+        <v>-2.399714</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.920078</v>
+        <v>-2.273203</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.73978</v>
+        <v>-0.877594</v>
       </c>
     </row>
     <row r="30">
@@ -2270,31 +2270,31 @@
         <v>2.046463</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.052743</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.279305</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.519138</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.519138</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.134917</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.332935</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.008665000000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.487558</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.540986</v>
       </c>
     </row>
     <row r="35">
@@ -2374,31 +2374,31 @@
         <v>2.198012</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.052743</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.279305</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.519138</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.519138</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.134917</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.332935</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.008665000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.487558</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.476594</v>
+        <v>1.01758</v>
       </c>
     </row>
     <row r="37">
@@ -2998,31 +2998,31 @@
         <v>0.132621</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.124026</v>
+        <v>0.071283</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.428753</v>
+        <v>0.149448</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.604993</v>
+        <v>0.085855</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.303844</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.260049</v>
+        <v>0.125132</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.785379</v>
+        <v>0.452444</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.220904</v>
+        <v>0.212239</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.8351460000000001</v>
+        <v>0.347588</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.661447</v>
+        <v>0.120461</v>
       </c>
     </row>
     <row r="49">
@@ -7093,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -28141,7 +28141,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -31479,7 +31483,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -32832,7 +32836,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -34559,7 +34563,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -38229,7 +38233,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -39410,7 +39414,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -41520,7 +41524,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
